--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46134.4980754978</v>
+        <v>46143.498072303366</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46143.498072303366</v>
+        <v>46157.498129502404</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46157.498129502404</v>
+        <v>46158.498127847444</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46158.498127847444</v>
+        <v>46159.498071169015</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46159.498071169015</v>
+        <v>46161.49807041651</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46161.49807041651</v>
+        <v>46163.49807340279</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46163.49807340279</v>
+        <v>46164.49807138881</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46164.49807138881</v>
+        <v>46166.49806814827</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46166.49806814827</v>
+        <v>46169.49806818273</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46169.49806818273</v>
+        <v>46171.49807101861</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46171.49807101861</v>
+        <v>46173.49807125004</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46173.49807125004</v>
+        <v>46174.4980698959</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46174.4980698959</v>
+        <v>46176.49807062512</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46176.49807062512</v>
+        <v>46177.49807122676</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46177.49807122676</v>
+        <v>46183.49806982651</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46183.49806982651</v>
+        <v>46192.49807445612</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46192.49807445612</v>
+        <v>46204.49807482632</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46204.49807482632</v>
+        <v>46205.49807252316</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46205.49807252316</v>
+        <v>46210.49807226844</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46210.49807226844</v>
+        <v>46213.498074745294</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46213.498074745294</v>
+        <v>46220.4980735071</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46220.4980735071</v>
+        <v>46221.49807334505</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46221.49807334505</v>
+        <v>46223.4980738312</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46223.4980738312</v>
+        <v>46224.498075868</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46224.498075868</v>
+        <v>46227.49806734966</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46227.49806734966</v>
+        <v>46231.498131435364</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46231.498131435364</v>
+        <v>46232.498072812334</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46232.498072812334</v>
+        <v>46233.498132604174</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46233.498132604174</v>
+        <v>46234.498130636755</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46234.498130636755</v>
+        <v>46235.498130960856</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46235.498130960856</v>
+        <v>46236.49813314807</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46236.49813314807</v>
+        <v>46237.49813270848</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46237.49813270848</v>
+        <v>46238.49813831039</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46238.49813831039</v>
+        <v>46240.4981209836</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/data_xlsx/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46240.4981209836</v>
+        <v>46245.49813525472</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>
